--- a/docs/data/sample.xlsx
+++ b/docs/data/sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\erenimo\projects\ses\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\erenimo\projects\ses\docs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC505BC6-1EA2-4A48-905B-F7485F148EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2194B86-C18D-4765-A5D0-C19589D6321D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="110">
   <si>
     <t>No_0833AB</t>
   </si>
@@ -131,78 +131,6 @@
     <t>25</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>Midterm(%25)_0833AB</t>
   </si>
   <si>
@@ -284,81 +212,6 @@
     <t>studentname24</t>
   </si>
   <si>
-    <t>studentname25</t>
-  </si>
-  <si>
-    <t>studentname26</t>
-  </si>
-  <si>
-    <t>studentname27</t>
-  </si>
-  <si>
-    <t>studentname28</t>
-  </si>
-  <si>
-    <t>studentname29</t>
-  </si>
-  <si>
-    <t>studentname30</t>
-  </si>
-  <si>
-    <t>studentname31</t>
-  </si>
-  <si>
-    <t>studentname32</t>
-  </si>
-  <si>
-    <t>studentname33</t>
-  </si>
-  <si>
-    <t>studentname34</t>
-  </si>
-  <si>
-    <t>studentname35</t>
-  </si>
-  <si>
-    <t>studentname36</t>
-  </si>
-  <si>
-    <t>studentname37</t>
-  </si>
-  <si>
-    <t>studentname38</t>
-  </si>
-  <si>
-    <t>studentname39</t>
-  </si>
-  <si>
-    <t>studentname40</t>
-  </si>
-  <si>
-    <t>studentname41</t>
-  </si>
-  <si>
-    <t>studentname42</t>
-  </si>
-  <si>
-    <t>studentname43</t>
-  </si>
-  <si>
-    <t>studentname44</t>
-  </si>
-  <si>
-    <t>studentname45</t>
-  </si>
-  <si>
-    <t>studentname46</t>
-  </si>
-  <si>
-    <t>studentname47</t>
-  </si>
-  <si>
-    <t>studentname48</t>
-  </si>
-  <si>
-    <t>studentname49</t>
-  </si>
-  <si>
     <t>studentsurname1</t>
   </si>
   <si>
@@ -431,81 +284,6 @@
     <t>studentsurname24</t>
   </si>
   <si>
-    <t>studentsurname25</t>
-  </si>
-  <si>
-    <t>studentsurname26</t>
-  </si>
-  <si>
-    <t>studentsurname27</t>
-  </si>
-  <si>
-    <t>studentsurname28</t>
-  </si>
-  <si>
-    <t>studentsurname29</t>
-  </si>
-  <si>
-    <t>studentsurname30</t>
-  </si>
-  <si>
-    <t>studentsurname31</t>
-  </si>
-  <si>
-    <t>studentsurname32</t>
-  </si>
-  <si>
-    <t>studentsurname33</t>
-  </si>
-  <si>
-    <t>studentsurname34</t>
-  </si>
-  <si>
-    <t>studentsurname35</t>
-  </si>
-  <si>
-    <t>studentsurname36</t>
-  </si>
-  <si>
-    <t>studentsurname37</t>
-  </si>
-  <si>
-    <t>studentsurname38</t>
-  </si>
-  <si>
-    <t>studentsurname39</t>
-  </si>
-  <si>
-    <t>studentsurname40</t>
-  </si>
-  <si>
-    <t>studentsurname41</t>
-  </si>
-  <si>
-    <t>studentsurname42</t>
-  </si>
-  <si>
-    <t>studentsurname43</t>
-  </si>
-  <si>
-    <t>studentsurname44</t>
-  </si>
-  <si>
-    <t>studentsurname45</t>
-  </si>
-  <si>
-    <t>studentsurname46</t>
-  </si>
-  <si>
-    <t>studentsurname47</t>
-  </si>
-  <si>
-    <t>studentsurname48</t>
-  </si>
-  <si>
-    <t>studentsurname49</t>
-  </si>
-  <si>
     <t>Project(%10)_0833AB</t>
   </si>
   <si>
@@ -584,76 +362,7 @@
     <t>221400050</t>
   </si>
   <si>
-    <t>221400051</t>
-  </si>
-  <si>
-    <t>221400052</t>
-  </si>
-  <si>
-    <t>221400053</t>
-  </si>
-  <si>
-    <t>221400054</t>
-  </si>
-  <si>
-    <t>221400055</t>
-  </si>
-  <si>
-    <t>221400056</t>
-  </si>
-  <si>
-    <t>221400057</t>
-  </si>
-  <si>
-    <t>221400058</t>
-  </si>
-  <si>
-    <t>221400059</t>
-  </si>
-  <si>
-    <t>221400060</t>
-  </si>
-  <si>
-    <t>221400061</t>
-  </si>
-  <si>
-    <t>221400062</t>
-  </si>
-  <si>
-    <t>221400063</t>
-  </si>
-  <si>
-    <t>221400064</t>
-  </si>
-  <si>
-    <t>221400065</t>
-  </si>
-  <si>
-    <t>221400066</t>
-  </si>
-  <si>
-    <t>221400067</t>
-  </si>
-  <si>
-    <t>221400068</t>
-  </si>
-  <si>
-    <t>221400069</t>
-  </si>
-  <si>
-    <t>221400070</t>
-  </si>
-  <si>
-    <t>221400071</t>
-  </si>
-  <si>
-    <t>221400072</t>
-  </si>
-  <si>
-    <t>221400073</t>
-  </si>
-  <si>
-    <t>221400074</t>
+    <t>differentName</t>
   </si>
 </sst>
 </file>
@@ -1987,16 +1696,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>6</v>
@@ -2007,13 +1716,13 @@
         <v>7</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
@@ -2022,20 +1731,16 @@
         <v>7</v>
       </c>
       <c r="G2" s="9">
-        <f t="shared" ref="G2:H50" ca="1" si="0">TRUNC(60 + ((RAND()*100 - 0) * (100 - 60) / (100 - 0)))</f>
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H2" s="9">
-        <f ca="1">TRUNC(60 + ((RAND()*100 - 0) * (100 - 60) / (100 - 0)))</f>
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I2" s="9">
-        <f ca="1">TRUNC(30 + ((RAND()*100 - 0) * (60 - 30) / (100 - 0)))</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J2" s="9">
-        <f ca="1">TRUNC(30 + ((RAND()*100 - 0) * (60 - 30) / (100 - 0)))</f>
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6"/>
     </row>
@@ -2044,13 +1749,13 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>8</v>
@@ -2059,20 +1764,16 @@
         <v>7</v>
       </c>
       <c r="G3" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="H3" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="I3" s="9">
-        <f t="shared" ref="I3:J50" ca="1" si="1">TRUNC(30 + ((RAND()*100 - 0) * (60 - 30) / (100 - 0)))</f>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -2081,13 +1782,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>10</v>
@@ -2096,20 +1797,16 @@
         <v>7</v>
       </c>
       <c r="G4" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="H4" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="I4" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="J4" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K4" s="8"/>
     </row>
@@ -2118,13 +1815,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>10</v>
@@ -2133,20 +1830,16 @@
         <v>7</v>
       </c>
       <c r="G5" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="H5" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K5" s="8"/>
     </row>
@@ -2155,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
@@ -2170,20 +1863,16 @@
         <v>7</v>
       </c>
       <c r="G6" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="H6" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I6" s="9">
-        <f t="shared" ca="1" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J6" s="9">
         <v>40</v>
-      </c>
-      <c r="J6" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>56</v>
       </c>
       <c r="K6" s="8"/>
     </row>
@@ -2192,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
@@ -2207,20 +1896,16 @@
         <v>7</v>
       </c>
       <c r="G7" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H7" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="I7" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K7" s="8"/>
     </row>
@@ -2229,13 +1914,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>10</v>
@@ -2244,20 +1929,16 @@
         <v>7</v>
       </c>
       <c r="G8" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="H8" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K8" s="8"/>
     </row>
@@ -2266,13 +1947,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>10</v>
@@ -2281,20 +1962,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K9" s="8"/>
     </row>
@@ -2303,13 +1980,13 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>10</v>
@@ -2318,20 +1995,16 @@
         <v>7</v>
       </c>
       <c r="G10" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H10" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="I10" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="8"/>
     </row>
@@ -2340,13 +2013,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>10</v>
@@ -2355,20 +2028,16 @@
         <v>7</v>
       </c>
       <c r="G11" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="H11" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K11" s="8"/>
     </row>
@@ -2377,13 +2046,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>10</v>
@@ -2392,20 +2061,16 @@
         <v>7</v>
       </c>
       <c r="G12" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="H12" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I12" s="9">
-        <f t="shared" ca="1" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J12" s="9">
         <v>40</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
       </c>
       <c r="K12" s="8"/>
     </row>
@@ -2414,13 +2079,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>10</v>
@@ -2429,20 +2094,16 @@
         <v>7</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K13" s="8"/>
     </row>
@@ -2451,13 +2112,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>10</v>
@@ -2466,20 +2127,16 @@
         <v>7</v>
       </c>
       <c r="G14" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="H14" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I14" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K14" s="8"/>
     </row>
@@ -2488,13 +2145,13 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>10</v>
@@ -2503,20 +2160,16 @@
         <v>7</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K15" s="8"/>
     </row>
@@ -2525,13 +2178,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>10</v>
@@ -2540,20 +2193,16 @@
         <v>7</v>
       </c>
       <c r="G16" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H16" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J16" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="K16" s="8"/>
     </row>
@@ -2562,13 +2211,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>10</v>
@@ -2577,20 +2226,16 @@
         <v>7</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K17" s="8"/>
     </row>
@@ -2599,13 +2244,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>8</v>
@@ -2614,20 +2259,16 @@
         <v>7</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="8"/>
     </row>
@@ -2636,13 +2277,13 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>10</v>
@@ -2651,20 +2292,16 @@
         <v>7</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K19" s="8"/>
     </row>
@@ -2673,13 +2310,13 @@
         <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>10</v>
@@ -2688,20 +2325,16 @@
         <v>7</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K20" s="8"/>
     </row>
@@ -2710,13 +2343,13 @@
         <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>10</v>
@@ -2725,20 +2358,16 @@
         <v>7</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K21" s="8"/>
     </row>
@@ -2747,13 +2376,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>8</v>
@@ -2762,20 +2391,16 @@
         <v>7</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K22" s="8"/>
     </row>
@@ -2784,13 +2409,13 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>10</v>
@@ -2799,19 +2424,15 @@
         <v>7</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" ca="1" si="1"/>
         <v>40</v>
       </c>
       <c r="K23" s="8"/>
@@ -2821,13 +2442,13 @@
         <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>10</v>
@@ -2836,20 +2457,16 @@
         <v>7</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K24" s="8"/>
     </row>
@@ -2858,13 +2475,13 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>10</v>
@@ -2873,20 +2490,16 @@
         <v>7</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K25" s="8"/>
     </row>
@@ -2895,13 +2508,13 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>10</v>
@@ -2910,909 +2523,329 @@
         <v>7</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>50</v>
-      </c>
+      <c r="A27" s="7"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
       <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="J28" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>45</v>
-      </c>
+      <c r="A28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
       <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="H29" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="J29" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>46</v>
-      </c>
+      <c r="A29" s="7"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>43</v>
-      </c>
+      <c r="A30" s="7"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="H31" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="I31" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="J31" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
+      <c r="A31" s="7"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
       <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="H32" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>92</v>
-      </c>
-      <c r="I32" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="J32" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>41</v>
-      </c>
+      <c r="A32" s="7"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
       <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>96</v>
-      </c>
-      <c r="H33" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="I33" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="J33" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>54</v>
-      </c>
+      <c r="A33" s="7"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="H34" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="I34" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>46</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>43</v>
-      </c>
+      <c r="A34" s="7"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
       <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="H35" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="I35" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="J35" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>57</v>
-      </c>
+      <c r="A35" s="7"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="H36" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="I36" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="J36" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>49</v>
-      </c>
+      <c r="A36" s="7"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
       <c r="K36" s="8"/>
     </row>
     <row r="37" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>89</v>
-      </c>
-      <c r="H37" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="I37" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="J37" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
-      </c>
+      <c r="A37" s="7"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="H38" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="I38" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="J38" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>59</v>
-      </c>
+      <c r="A38" s="7"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
       <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="H39" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="I39" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="J39" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>42</v>
-      </c>
+      <c r="A39" s="7"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="H40" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="I40" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="J40" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
+      <c r="A40" s="7"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
       <c r="K40" s="8"/>
     </row>
     <row r="41" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="H41" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="I41" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="J41" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>57</v>
-      </c>
+      <c r="A41" s="7"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="H42" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="I42" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="J42" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>49</v>
-      </c>
+      <c r="A42" s="7"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
       <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="H43" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="I43" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="J43" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
+      <c r="A43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
       <c r="K43" s="8"/>
     </row>
     <row r="44" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="H44" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="I44" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="J44" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>54</v>
-      </c>
+      <c r="A44" s="7"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
       <c r="K44" s="8"/>
     </row>
     <row r="45" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="H45" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>89</v>
-      </c>
-      <c r="I45" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="J45" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>30</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
       <c r="K45" s="8"/>
     </row>
     <row r="46" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="H46" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="I46" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="J46" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
+      <c r="A46" s="7"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
       <c r="K46" s="8"/>
     </row>
     <row r="47" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="H47" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>92</v>
-      </c>
-      <c r="I47" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="J47" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
+      <c r="A47" s="7"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="H48" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>89</v>
-      </c>
-      <c r="I48" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="J48" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>57</v>
-      </c>
+      <c r="A48" s="7"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
       <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="H49" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>67</v>
-      </c>
-      <c r="I49" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="J49" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>48</v>
-      </c>
+      <c r="A49" s="7"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="H50" s="9">
-        <f t="shared" ca="1" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="I50" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="J50" s="9">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
-      </c>
+      <c r="A50" s="7"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
       <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
